--- a/docs/review_docs/reviews.xlsx
+++ b/docs/review_docs/reviews.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EffortsEngineers\docs\review_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09CF5F5B-7B5A-4F27-BB7F-974B3683ABE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9CC440-BB42-4B1B-B643-29B22D8B8C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F9EDE7E4-E603-4711-B536-EF9112E52C44}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F9EDE7E4-E603-4711-B536-EF9112E52C44}"/>
   </bookViews>
   <sheets>
     <sheet name="defects" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="115">
   <si>
     <t>Efforts Engineers Website – List of Changes</t>
   </si>
@@ -390,6 +390,15 @@
   </si>
   <si>
     <t>Efforts Engineers – Your Trusted Partner for Air &amp; Refrigeration Compressor Parts, Valves &amp; Technical Solutions.</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>pASS</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
 </sst>
 </file>
@@ -816,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475BC002-663F-4F31-A8CF-DE9ECF1F0D24}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.1796875" style="1" customWidth="1"/>
@@ -824,20 +833,23 @@
     <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="C2" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -845,7 +857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -853,44 +865,59 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="C5" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="C6" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="C7" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C8" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
